--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486896_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486896_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5126</v>
+        <v>5.2292</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5162</v>
+        <v>4.1438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9964</v>
+        <v>1.0853</v>
       </c>
       <c r="G2" t="n">
         <v>4.4688</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3669</v>
+        <v>0.3497</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9222</v>
+        <v>-0.2946</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5554</v>
+        <v>0.6443</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4932</v>
+        <v>3.9669</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5927</v>
+        <v>2.8086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9005</v>
+        <v>1.1583</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0017</v>
+        <v>4.9959</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7625999999999999</v>
+        <v>1.4888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2391</v>
+        <v>3.5071</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1719</v>
+        <v>3.8664</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4224</v>
+        <v>0.3149</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2506</v>
+        <v>3.5516</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8298</v>
+        <v>1.1295</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3401</v>
+        <v>1.174</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4897</v>
+        <v>-0.0445</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7871</v>
+        <v>0.4166</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7699</v>
+        <v>0.1742</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0172</v>
+        <v>0.2423</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5277</v>
+        <v>-0.8295</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1786</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.28</v>
+        <v>2.2372</v>
       </c>
       <c r="E4" t="n">
-        <v>2.181</v>
+        <v>1.8905</v>
       </c>
       <c r="F4" t="n">
-        <v>1.099</v>
+        <v>0.3468</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9959</v>
+        <v>2.0909</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4888</v>
+        <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5071</v>
+        <v>2.0653</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8664</v>
+        <v>2.2083</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3149</v>
+        <v>0.3538</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5516</v>
+        <v>1.8545</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1295</v>
+        <v>-0.1174</v>
       </c>
       <c r="N4" t="n">
-        <v>1.174</v>
+        <v>-0.3281</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0445</v>
+        <v>0.2107</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2703</v>
+        <v>1.173</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4534</v>
+        <v>0.9142</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1831</v>
+        <v>0.2588</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3401</v>
+        <v>2.1473</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7859</v>
+        <v>1.1283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5543</v>
+        <v>1.019</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0909</v>
+        <v>1.0017</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0257</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0653</v>
+        <v>0.2391</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2083</v>
+        <v>0.1719</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3538</v>
+        <v>0.4224</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8545</v>
+        <v>-0.2506</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1174</v>
+        <v>0.8298</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3281</v>
+        <v>0.3401</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2107</v>
+        <v>0.4897</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2759</v>
+        <v>1.4413</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8096</v>
+        <v>1.3055</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4663</v>
+        <v>0.1358</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.5277</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9075</v>
+        <v>1.9685</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6117</v>
+        <v>0.8209</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2958</v>
+        <v>1.1476</v>
       </c>
       <c r="G6" t="n">
         <v>2.8272</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2769</v>
+        <v>-0.2159</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4534</v>
+        <v>-0.2442</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1765</v>
+        <v>0.0283</v>
       </c>
       <c r="V6" t="n">
         <v>0.5893</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7148</v>
+        <v>1.4641</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7063</v>
+        <v>1.9836</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0085</v>
+        <v>-0.5196</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4784</v>
+        <v>0.3037</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6283</v>
+        <v>0.0516</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1499</v>
+        <v>0.2521</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1852</v>
+        <v>2.0419</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0122</v>
+        <v>1.1874</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1974</v>
+        <v>0.8545</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6636</v>
+        <v>-1.7382</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6161</v>
+        <v>-1.1358</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0475</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9222</v>
+        <v>0.339</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3021</v>
+        <v>-0.0582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6201</v>
+        <v>0.3973</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0775</v>
+        <v>1.4184</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3305</v>
+        <v>0.7063</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.253</v>
+        <v>0.7121</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2298</v>
+        <v>0.4784</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9402</v>
+        <v>1.6283</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2897</v>
+        <v>-1.1499</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1365</v>
+        <v>-0.1852</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2683</v>
+        <v>1.0122</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8682</v>
+        <v>-1.1974</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9067</v>
+        <v>0.6636</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3281</v>
+        <v>0.6161</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5786</v>
+        <v>0.0475</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8046</v>
+        <v>0.6258</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9989</v>
+        <v>0.3021</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8057</v>
+        <v>0.3237</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2875</v>
+        <v>0.1088</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4805</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7679</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6726</v>
+        <v>0.166</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2514</v>
+        <v>1.3741</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5788</v>
+        <v>-1.2081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3037</v>
+        <v>1.6955</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0516</v>
+        <v>1.6771</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2521</v>
+        <v>0.0184</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0419</v>
+        <v>2.5132</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1874</v>
+        <v>1.8687</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8545</v>
+        <v>0.6445</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7382</v>
+        <v>-0.8177</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1358</v>
+        <v>-0.1917</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.6261</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4525</v>
+        <v>0.2179</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7905</v>
+        <v>0.0929</v>
       </c>
       <c r="U9" t="n">
-        <v>0.338</v>
+        <v>0.125</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1677</v>
+        <v>0.1653</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5833</v>
+        <v>-0.0711</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4156</v>
+        <v>0.2364</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6955</v>
+        <v>1.696</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6771</v>
+        <v>1.5829</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0184</v>
+        <v>0.113</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5132</v>
+        <v>2.4632</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8687</v>
+        <v>1.9111</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6445</v>
+        <v>0.5522</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8177</v>
+        <v>-0.7672</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1917</v>
+        <v>-0.3281</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6261</v>
+        <v>-0.4391</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2197</v>
+        <v>0.0504</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3021</v>
+        <v>-0.1667</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0825</v>
+        <v>0.2171</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7207</v>
+        <v>-0.3491</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7207</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0484</v>
+        <v>0.0018</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0139</v>
+        <v>1.2844</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0345</v>
+        <v>-1.2826</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5029</v>
+        <v>2.2298</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.07140000000000001</v>
+        <v>1.9402</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4314</v>
+        <v>0.2897</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1179</v>
+        <v>3.1365</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0389</v>
+        <v>2.2683</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0789</v>
+        <v>0.8682</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6208</v>
+        <v>-0.9067</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1104</v>
+        <v>-0.3281</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5104</v>
+        <v>-0.5786</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4545</v>
+        <v>1.7289</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>0.9529</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5863</v>
+        <v>0.776</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2875</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6089</v>
+        <v>-0.2559</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4895</v>
+        <v>-0.0139</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1193</v>
+        <v>-0.242</v>
       </c>
       <c r="G12" t="n">
-        <v>1.696</v>
+        <v>-0.5029</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5829</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.113</v>
+        <v>-0.4314</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4632</v>
+        <v>0.1179</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9111</v>
+        <v>0.0389</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5522</v>
+        <v>0.0789</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7672</v>
+        <v>-0.6208</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3281</v>
+        <v>-0.1104</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4391</v>
+        <v>-0.5104</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7237</v>
+        <v>0.247</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5851</v>
+        <v>-0.1317</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1386</v>
+        <v>0.3788</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.5087</v>
+        <v>18.5088</v>
       </c>
       <c r="E13" t="n">
-        <v>16.0556</v>
+        <v>16.0555</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4533</v>
+        <v>2.4532</v>
       </c>
       <c r="G13" t="n">
         <v>21.285</v>
@@ -1453,10 +1453,10 @@
         <v>-3.0434</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1905999999999999</v>
+        <v>0.1906000000000002</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.234</v>
+        <v>-3.233999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-5.1335</v>
@@ -1465,19 +1465,19 @@
         <v>-12.3207</v>
       </c>
       <c r="R13" t="n">
-        <v>7.186900000000001</v>
+        <v>7.1869</v>
       </c>
       <c r="S13" t="n">
-        <v>6.373700000000001</v>
+        <v>6.3737</v>
       </c>
       <c r="T13" t="n">
-        <v>2.846299999999999</v>
+        <v>2.8464</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5275</v>
+        <v>3.5274</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.0164</v>
+        <v>-4.016400000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.2012</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3957</v>
+        <v>0.9536</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5393</v>
+        <v>2.9577</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1436</v>
+        <v>-2.0041</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5539</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8718</v>
+        <v>-0.3139</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6046</v>
+        <v>-0.1862</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2672</v>
+        <v>-0.1277</v>
       </c>
       <c r="V14" t="n">
         <v>1.1786</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1361</v>
+        <v>0.5522</v>
       </c>
       <c r="E15" t="n">
-        <v>0.108</v>
+        <v>3.2494</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2441</v>
+        <v>-2.6971</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0279</v>
+        <v>-3.145</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4216</v>
+        <v>-0.461</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4495</v>
+        <v>-2.684</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1156</v>
+        <v>0.7136</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9183</v>
+        <v>1.1485</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1973</v>
+        <v>-0.4349</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1435</v>
+        <v>-3.8586</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4967</v>
+        <v>-1.6094</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6468</v>
+        <v>-2.2492</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7132</v>
+        <v>-1.1672</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2512</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.462</v>
+        <v>-0.4812</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3.427</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.427</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2719</v>
+        <v>-0.182</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4021</v>
+        <v>0.0251</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.674</v>
+        <v>-0.2071</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5709</v>
+        <v>-0.6391</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3395</v>
+        <v>-0.2077</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2314</v>
+        <v>-0.4314</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5305</v>
+        <v>0.1763</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4385</v>
+        <v>0.0973</v>
       </c>
       <c r="L16" t="n">
-        <v>0.092</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1014</v>
+        <v>-0.8154</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.778</v>
+        <v>-0.305</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3234</v>
+        <v>-0.5104</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0295</v>
+        <v>0.0465</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0195</v>
+        <v>-0.1512</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.01</v>
+        <v>0.1976</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2724</v>
+        <v>-0.3626</v>
       </c>
       <c r="E17" t="n">
-        <v>2.831</v>
+        <v>0.1929</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.1034</v>
+        <v>-0.5555</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.145</v>
+        <v>-1.5709</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.461</v>
+        <v>-1.3395</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.684</v>
+        <v>-0.2314</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7136</v>
+        <v>0.5305</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1485</v>
+        <v>0.4385</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4349</v>
+        <v>0.092</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8586</v>
+        <v>-2.1014</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6094</v>
+        <v>-1.778</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2492</v>
+        <v>-0.3234</v>
       </c>
       <c r="P17" t="n">
         <v>1.4374</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9919</v>
+        <v>-0.1202</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1044</v>
+        <v>-0.2287</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8875</v>
+        <v>0.1086</v>
       </c>
       <c r="V17" t="n">
-        <v>3.427</v>
+        <v>-0.1088</v>
       </c>
       <c r="W17" t="n">
-        <v>3.427</v>
+        <v>-0.1088</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4052</v>
+        <v>-1.3844</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0795</v>
+        <v>-1.0426</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3257</v>
+        <v>-0.3418</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6391</v>
+        <v>-1.0279</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2077</v>
+        <v>0.4216</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4314</v>
+        <v>-1.4495</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1763</v>
+        <v>1.1156</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0973</v>
+        <v>0.9183</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789</v>
+        <v>0.1973</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8154</v>
+        <v>-2.1435</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.305</v>
+        <v>-0.4967</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5104</v>
+        <v>-1.6468</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1767</v>
+        <v>0.4649</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2558</v>
+        <v>0.1005</v>
       </c>
       <c r="U18" t="n">
-        <v>0.079</v>
+        <v>0.3643</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3441</v>
+        <v>-2.0251</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3021</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4369</v>
+        <v>-2.3271</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5309</v>
@@ -1936,13 +1936,13 @@
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1705</v>
+        <v>-0.8515</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7441</v>
+        <v>-0.5349</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4264</v>
+        <v>-0.3166</v>
       </c>
       <c r="V19" t="n">
         <v>1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7056</v>
+        <v>-2.4861</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2682</v>
+        <v>-0.536</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4374</v>
+        <v>-1.9501</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0347</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0467</v>
+        <v>-0.8272</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2438</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1971</v>
+        <v>-0.3155</v>
       </c>
       <c r="V20" t="n">
         <v>0.3491</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4199</v>
+        <v>-3.6448</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3023</v>
+        <v>-0.6162</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1175</v>
+        <v>-3.0286</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9634</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2778</v>
+        <v>-0.5027</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1704</v>
+        <v>-0.1434</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4482</v>
+        <v>-0.3593</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7679</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6651</v>
+        <v>-4.0096</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5707</v>
+        <v>-3.1523</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0944</v>
+        <v>-0.8573</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7925</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0698</v>
+        <v>-1.4142</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2516</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8182</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6842</v>
+        <v>-5.2229</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2058</v>
+        <v>-3.8334</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4784</v>
+        <v>-1.3894</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0266</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4522</v>
+        <v>-0.9909</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2749</v>
+        <v>-0.3527</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7271</v>
+        <v>-0.6382</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.5088</v>
+        <v>-17.8117</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4533</v>
+        <v>-2.453299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.0554</v>
+        <v>-15.3581</v>
       </c>
       <c r="G24" t="n">
         <v>-21.2849</v>
@@ -2296,16 +2296,16 @@
         <v>-14.2081</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.076999999999999</v>
+        <v>-7.077</v>
       </c>
       <c r="J24" t="n">
-        <v>3.0435</v>
+        <v>3.043499999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-0.1903999999999997</v>
       </c>
       <c r="L24" t="n">
-        <v>3.2339</v>
+        <v>3.233899999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-24.3283</v>
@@ -2326,13 +2326,13 @@
         <v>12.3206</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.3737</v>
+        <v>-5.6764</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.5273</v>
+        <v>-3.5274</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.8465</v>
+        <v>-2.1491</v>
       </c>
       <c r="V24" t="n">
         <v>4.016400000000001</v>
